--- a/data/high_low.xlsx
+++ b/data/high_low.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.7908</v>
+        <v>4.790752380952381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.3533</v>
+        <v>4.35332</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5977</v>
+        <v>4.597733333333333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.28</v>
+        <v>4.27999</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.3353</v>
+        <v>5.33532380952381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.0006</v>
+        <v>5.000565</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.3033</v>
+        <v>4.303347619047619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.9585</v>
+        <v>3.958525</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.7645</v>
+        <v>2.764457142857143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.5975</v>
+        <v>2.597471428571429</v>
       </c>
     </row>
     <row r="7">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1169</v>
+        <v>0.1169181818181818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0992</v>
+        <v>0.09918666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4013</v>
+        <v>0.4013190476190476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3683</v>
+        <v>0.3683047619047619</v>
       </c>
     </row>
   </sheetData>
